--- a/data/curriculo_unicafam/mig_propuestas/ofertas_academicas_mig_consolidado.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/ofertas_academicas_mig_consolidado.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Electiva de Profundización (Pregrado) - Certificado de Profundización en Cloud Data &amp; MLOps</t>
+          <t>Electiva de Profundización (Pregrado) - Certificado de Profundización en Cloud Data Engineering &amp; MLOps</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Sábados de 8:00 a.m. a 1:00 p.m. / Sesiones sincrónicas</t>
+          <t>Sábados de 7:00 a.m. a 1:00 p.m. / Sesiones sincrónicas virtuales y laboratorios presenciales bimensuales</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Próximo inicio de cohorte académica</t>
+          <t>Febrero de 2025</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Al completar el número total de horas del programa</t>
+          <t>Junio de 2025</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Por definir según tarifario institucional</t>
+          <t>$2.950.000 COP</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Descuento especial comunidad UniCafam / Afiliados Cafam</t>
+          <t>$2.212.500 COP (25% dcto afiliados/estudiantes)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Tarifa preferencial egresados UniCafam</t>
+          <t>$2.360.000 COP (20% dcto)</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Tarifa corporativa por volumen (&gt;3 inscritos)</t>
+          <t>$2.065.000 COP (por convenio empresarial &gt;3 personas)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -836,7 +836,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Cohortes semestrales continuas</t>
+          <t>Cohortes en el primer y segundo semestre de cada año académico</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>El presente programa responde a las demandas urgentes del mercado laboral identificadas por el Observatorio de Inteligencia Laboral de UniCafam. El análisis de vacantes revela una brecha del sector productivo en competencias de Implementación de Arquitecturas Cloud y MLOps. El impacto salarial proyectado (+45% de incremento salarial al acceder a roles de infraestructura cloud.) sustenta la pertinencia de formar talento especializado con alta tasa de empleabilidad y proyección nacional e internacional.</t>
+          <t>La tecnología en Análisis y Gestión de Datos de UniCafam forma tecnólogos con excelente dominio de análisis predictivo, Python y SQL. Sin embargo, para acceder a vacantes de alta remuneración, estos profesionales deben operar en la nube y automatizar el ciclo de vida de los modelos. Según el observatorio, AWS y GCP registran un porcentaje de penetración conjunto de más del 32% en la demanda y salarios de hasta $15M COP. Introducir una electiva de 6 créditos en el último año de la tecnología y articulación profesional asegura que el estudiante no solo construya modelos (lo que ya hace muy bien), sino que aprenda a empaquetarlos, desplegarlos y monitorearlos. Esto duplica de inmediato el espectro de empleabilidad hacia roles de Junior Cloud Engineer y MLOps Practitioner, apalancando la prima salarial internacional.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -898,9 +898,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Desarrollar competencias especializadas en Implementación de Arquitecturas Cloud y MLOps para responder a los desafíos tecnológicos del mercado.
-• Implementar soluciones técnicas reales mediante proyectos aplicados utilizando herramientas líderes de la industria.
-• Integrar metodologías ágiles y estándares internacionales en el ciclo de vida de los datos e inteligencia artificial.</t>
+          <t>• Objetivo General: Desarrollar competencias teórico-prácticas en la estructuración de flujos de datos automatizados y despliegue continuo de modelos de Machine Learning en entornos de computación en la nube empresariales.
+• Objetivo Específico 1: Implementar arquitecturas de almacenamiento y procesamiento serverless en AWS y GCP para canalizar volúmenes de datos a escala.
+• Objetivo Específico 2: Contenedorizar aplicaciones de IA utilizando Docker y desplegar microservicios eficientes accesibles a través de APIs web.
+• Objetivo Específico 3: Diseñar ciclos de vida automatizados de modelos (MLOps) integrando herramientas de tracking como MLflow y pipelines básicos de CI/CD.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -944,7 +945,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Estudiantes de últimos semestres de Tecnología en Análisis de Datos con bases en Python y SQL.</t>
+          <t>Estudiantes de 5to semestre de la Tecnología en Análisis y Gestión de Datos, estudiantes de Ingeniería de Sistemas de UniCafam y egresados tecnólogos de datos que dominen Python intermedio y bases de datos relacionales.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -979,7 +980,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Metodología 100% teórico-práctica con enfoque en Aprendizaje Basado en Retos y Proyectos Reales (PBL). Las sesiones combinan fundamentación conceptual, laboratorios guiados en la nube y trabajo autónomo con acompañamiento de expertos de la industria. Cada módulo concluye con un entregable técnico aplicable.</t>
+          <t>Modelo pedagógico activo basado en retos (PBL - Project Based Learning). Los estudiantes desarrollarán un proyecto integrador a lo largo del semestre consistente en tomar un modelo predictivo previamente entrenado en su carrera, empaquetarlo en un contenedor Docker, desplegarlo como microservicio en AWS, y configurar su respectivo pipeline de control, monitoreo y CI/CD utilizando GitHub Actions y MLflow. Las clases constan de un 30% de conceptualización y un 70% de talleres aplicados en laboratorios cloud (AWS Academy y Google Cloud for Education).</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1023,10 +1024,9 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Alineación directa con los requisitos reales de vacantes analizadas en el Observatorio Laboral.
-✔ Enfoque en tecnologías de alta prima salarial (+45% de incremento salarial al acceder a roles de infraestructura cloud.).
-✔ Certificación institucional respaldada por la Fundación Universitaria Cafam.
-✔ Docentes activos y líderes técnicos en empresas multinacionales de tecnología.</t>
+          <t>✔ Acceso gratuito a entornos sandbox de AWS y Google Cloud a través de convenios educativos de UniCafam.
+✔ Voucher de descuento de hasta el 50% para la certificación oficial AWS Certified Cloud Practitioner o GCP Associate Cloud Engineer.
+✔ Desarrollo de un portafolio de producción alojado en GitHub listo para ser presentado en procesos de selección internacional.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1119,23 +1119,22 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Arquitecturas de Datos en la Nube (AWS &amp; GCP)</t>
+          <t>Cloud Data Engineering (AWS &amp; GCP Foundations)</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Unidades Temáticas:
-1. Fundamentación y Arquitectura.
-2. Implementación Práctica y Laboratorios (AWS S3, AWS Glue, Google Cloud Storage, BigQuery).
-3. Proyecto de Aplicación y Evaluación.
-Resultados de Aprendizaje:
-Configurar entornos de almacenamiento y procesamiento de datos en la nube utilizando servicios gestionados de AWS y GCP. [Stack: AWS S3, AWS Glue, Google Cloud Storage, BigQuery]</t>
+          <t>1. Fundamentos de nube e Infraestructura Global.
+2. Almacenamiento de datos escalable en AWS (S3) y GCP (Cloud Storage).
+3. Bases de datos modernas y Data Warehousing (Amazon Redshift, Google BigQuery).
+4. Orquestación serverless y ETL en la nube (AWS Glue, Cloud Dataflow).
+5. Seguridad, gobernanza de datos y manejo de accesos (IAM). [Stack: AWS S3, Google Cloud Storage, BigQuery, AWS Glue, IAM]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Módulo 1 - Semanas 1 a 4</t>
+          <t>Semanas 1 a 8</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
@@ -1169,23 +1168,22 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Automatización y Ciclo de Vida de Modelos (MLOps)</t>
+          <t>MLOps &amp; Despliegue de Modelos de IA</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>Unidades Temáticas:
-1. Fundamentación y Arquitectura.
-2. Implementación Práctica y Laboratorios (Docker, Git, MLflow, CI/CD Pipelines).
-3. Proyecto de Aplicación y Evaluación.
-Resultados de Aprendizaje:
-Diseñar flujos de trabajo automatizados para el entrenamiento, despliegue y monitoreo de modelos de aprendizaje automático. [Stack: Docker, Git, MLflow, CI/CD Pipelines]</t>
+          <t>1. Introducción al ciclo de vida de MLOps y comparación con DevOps.
+2. Creación de APIs web para consumo de modelos (FastAPI, Flask).
+3. Contenedorización de aplicaciones y entornos aislados de desarrollo con Docker.
+4. Tracking de experimentos, almacenamiento de artefactos y registro de modelos con MLflow.
+5. Monitoreo básico del comportamiento del modelo en producción (Data Drift e inferencia). [Stack: Docker, FastAPI, MLflow, GitHub Actions]</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t>Módulo 2 - Semanas 5 a 8</t>
+          <t>Semanas 9 a 16</t>
         </is>
       </c>
       <c r="H42" s="21" t="inlineStr">
@@ -1251,18 +1249,18 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Especialista / Magíster en AWS S3</t>
+          <t>Especialista en Infraestructura de Datos Cloud</t>
         </is>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Arquitecturas de Datos en la Nube (AWS &amp; GCP)</t>
+          <t>Cloud Data Engineering (AWS &amp; GCP Foundations)</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>Profesional con más de 5 años de experiencia liderando proyectos de Arquitecturas de Datos en la Nube (AWS &amp; GCP) en el sector productivo, con certificaciones internacionales en el stack tecnológico enseñado.</t>
+          <t>Ingeniero de Sistemas o de Datos con especialización o maestría en áreas afines, certificado oficialmente como AWS Certified Solutions Architect o GCP Professional Cloud Architect, con experiencia laboral mínima de 4 años en el sector corporativo diseñando pipelines en la nube.</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1281,18 +1279,18 @@
       <c r="B50" s="17" t="inlineStr"/>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Especialista / Magíster en Docker</t>
+          <t>Ingeniero de Plataformas AI / MLOps Lead</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="22" t="inlineStr">
         <is>
-          <t>Automatización y Ciclo de Vida de Modelos (MLOps)</t>
+          <t>MLOps &amp; Despliegue de Modelos de IA</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>Profesional con más de 5 años de experiencia liderando proyectos de Automatización y Ciclo de Vida de Modelos (MLOps) en el sector productivo, con certificaciones internacionales en el stack tecnológico enseñado.</t>
+          <t>Científico de Datos Senior o MLOps Engineer con experiencia laboral de más de 5 años en despliegue de modelos a gran escala, dominio experto en metodologías ágiles de ingeniería de software, empaquetamiento con Docker y orquestadores.</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1470,7 +1468,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>BUSINESS INTELLIGENCE AVANZADO &amp; DATA STORYTELLING</t>
+          <t>IA GENERATIVA Y ARQUITECTURAS RAG PARA NEGOCIOS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -1487,7 +1485,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Microcredencial / Certificación Corta (Educación Continua) - Certificación en Analítica de Negocios con Power BI</t>
+          <t>Microcredencial / Certificación Corta (Educación Continua / Formación Avanzada) - Certificación Universitaria de Especialista en IA Generativa &amp; Arquitecturas RAG para Negocios</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -1504,7 +1502,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Sábados de 8:00 a.m. a 1:00 p.m. / Sesiones sincrónicas</t>
+          <t>Martes y Jueves de 6:00 p.m. a 9:00 p.m. (Virtual Sincrónico)</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -1538,7 +1536,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Próximo inicio de cohorte académica</t>
+          <t>Abril de 2025</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -1555,7 +1553,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Al completar el número total de horas del programa</t>
+          <t>Junio de 2025</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -1577,7 +1575,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Por definir según tarifario institucional</t>
+          <t>$1.500.000 COP</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -1594,7 +1592,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Descuento especial comunidad UniCafam / Afiliados Cafam</t>
+          <t>$1.125.000 COP (25% dcto)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -1611,7 +1609,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Tarifa preferencial egresados UniCafam</t>
+          <t>$1.200.000 COP (20% dcto)</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -1628,7 +1626,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Tarifa corporativa por volumen (&gt;3 inscritos)</t>
+          <t>$1.050.000 COP (por convenio empresarial &gt;3 personas)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -1644,7 +1642,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Cohortes semestrales continuas</t>
+          <t>Tres ediciones anuales planificadas (Febrero, Junio, Septiembre)</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -1662,7 +1660,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>El presente programa responde a las demandas urgentes del mercado laboral identificadas por el Observatorio de Inteligencia Laboral de UniCafam. El análisis de vacantes revela una brecha del sector productivo en competencias de Business Intelligence Avanzado &amp; Data Storytelling. El impacto salarial proyectado (Aumento inmediato de empleabilidad en roles de analítica de negocios local.) sustenta la pertinencia de formar talento especializado con alta tasa de empleabilidad y proyección nacional e internacional.</t>
+          <t>La revolución de la Inteligencia Artificial Generativa y los Modelos de Lenguaje de Gran Escala (LLMs) ha transformado la demanda empresarial. Los egresados de UniCafam cuentan con sólidas competencias en Procesamiento de Lenguaje Natural (NLP) tradicional gracias a la materia 'Procesamiento de Texto y Técnicas de Información'. Esta microcredencial tiende un puente directo hacia las tecnologías más modernas de IA de Frontera: Retrieval-Augmented Generation (RAG) y bases de datos vectoriales. Conectando lo que ya saben de procesamiento de texto con LLMs comerciales y de código abierto (Llama, OpenAI, Claude), el egresado se transforma en un desarrollador de soluciones cognitivas inteligentes que automatizan la búsqueda de información corporativa, impulsando su empleabilidad en un mercado que valora estas competencias en niveles sumamente altos.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -1706,9 +1704,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Desarrollar competencias especializadas en Business Intelligence Avanzado &amp; Data Storytelling para responder a los desafíos tecnológicos del mercado.
-• Implementar soluciones técnicas reales mediante proyectos aplicados utilizando herramientas líderes de la industria.
-• Integrar metodologías ágiles y estándares internacionales en el ciclo de vida de los datos e inteligencia artificial.</t>
+          <t>• Objetivo General: Capacitar en el diseño, desarrollo e integración de sistemas de IA Generativa empresariales utilizando arquitecturas RAG para optimizar la toma de decisiones y la automatización de procesos de consulta.
+• Objetivo Específico 1: Utilizar frameworks avanzados de desarrollo (LangChain e Indexadores) para orquestar flujos cognitivos complejos basados en LLMs.
+• Objetivo Específico 2: Implementar bases de datos vectoriales para el almacenamiento de embeddings semánticos optimizados.
+• Objetivo Específico 3: Diseñar aplicaciones web que utilicen técnicas de Prompt Engineering avanzado y agentes inteligentes autónomos.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -1752,7 +1751,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Profesionales o técnicos con conocimiento básico de Excel y manejo de datos.</t>
+          <t>Científicos de datos, tecnólogos en análisis de datos, ingenieros de desarrollo de software, analistas de BI senior y entusiastas de la tecnología con nociones lógicas de programación en Python.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -1787,7 +1786,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Metodología 100% teórico-práctica con enfoque en Aprendizaje Basado en Retos y Proyectos Reales (PBL). Las sesiones combinan fundamentación conceptual, laboratorios guiados en la nube y trabajo autónomo con acompañamiento de expertos de la industria. Cada módulo concluye con un entregable técnico aplicable.</t>
+          <t>Enfoque de taller práctico hands-on. Cada sesión sincrónica introduce un reto técnico real de la industria (p. ej., construir un chatbot que responda preguntas basadas exclusivamente en los manuales de procedimientos de una empresa). Los laboratorios se desarrollan sobre cuadernos de Jupyter de Google Colab utilizando APIs comerciales y modelos open-source de Hugging Face. Se utiliza un canal continuo de comunicación en Discord para mentorías personalizadas de código.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1831,10 +1830,9 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Alineación directa con los requisitos reales de vacantes analizadas en el Observatorio Laboral.
-✔ Enfoque en tecnologías de alta prima salarial (Aumento inmediato de empleabilidad en roles de analítica de negocios local.).
-✔ Certificación institucional respaldada por la Fundación Universitaria Cafam.
-✔ Docentes activos y líderes técnicos en empresas multinacionales de tecnología.</t>
+          <t>✔ Inclusión en el portafolio institucional de microcredenciales digitales insignias de UniCafam con estándar internacional OpenBadges para compartir en LinkedIn.
+✔ Acceso directo a la comunidad de expertos en Inteligencia Artificial de la escuela de Ingeniería UniCafam.
+✔ Plantillas de código listas para producción en entornos empresariales.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1927,28 +1925,30 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Modelamiento DAX y Visualización de Impacto</t>
+          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Unidades Temáticas:
-1. Fundamentación y Arquitectura.
-2. Implementación Práctica y Laboratorios (Power BI, DAX, Power Query).
-3. Proyecto de Aplicación y Evaluación.
-Resultados de Aprendizaje:
-Construir modelos de datos relacionales y medidas complejas utilizando el lenguaje DAX para resolver problemas de negocio. [Stack: Power BI, DAX, Power Query]</t>
+          <t>1. Introducción a la IA Generativa, Modelos Fundacionales y Transformers.
+2. Fundamentos de Embeddings: Conversión de texto a vectores densos.
+3. Bases de Datos Vectoriales: Almacenamiento, indexación y búsqueda en Pinecone, ChromaDB y Qdrant.
+4. El flujo RAG (Retrieval-Augmented Generation): Conexión de documentos privados con LLMs.
+5. Frameworks de Orquestación: Construcción paso a paso con LangChain y LlamaIndex.
+6. Prompt Engineering Avanzado, técnicas Few-Shot y control de alucinaciones.
+7. Agentes autónomos de IA que interactúan con APIs externas y SQL corporativo.
+8. Despliegue de un prototipo interactivo utilizando Streamlit. [Stack: LangChain, Pinecone, ChromaDB, OpenAI API, Hugging Face, Streamlit]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Módulo 1 - Semanas 1 a 4</t>
+          <t>Semanas 1 a 8</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>96 h</t>
         </is>
       </c>
     </row>
@@ -2009,18 +2009,18 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Especialista / Magíster en Power BI</t>
+          <t>Investigador / Ingeniero Senior en NLP &amp; IA Generativa</t>
         </is>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Modelamiento DAX y Visualización de Impacto</t>
+          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Profesional con más de 5 años de experiencia liderando proyectos de Modelamiento DAX y Visualización de Impacto en el sector productivo, con certificaciones internacionales en el stack tecnológico enseñado.</t>
+          <t>Profesional en Ingeniería de Sistemas, Inteligencia Artificial o Ciencia de Datos, con Maestría o Doctorado en Inteligencia Artificial o Computación Cognitiva, con publicaciones científicas o experiencia de mínimo 3 años desarrollando productos basados en tecnologías Transformers y modelos GPT.</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -2093,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H46"/>
+  <dimension ref="B1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Especialización Universitaria (Posgrado) - Especialista en Ingeniería de Datos</t>
+          <t>Especialización Universitaria (Posgrado) - Especialista en Ingeniería de Datos y Arquitecturas Cloud</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Sábados de 8:00 a.m. a 1:00 p.m. / Sesiones sincrónicas</t>
+          <t>Viernes de 5:00 p.m. a 10:00 p.m. y Sábados de 8:00 a.m. a 2:00 p.m.</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Próximo inicio de cohorte académica</t>
+          <t>Julio de 2025</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Al completar el número total de horas del programa</t>
+          <t>Junio de 2026</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Por definir según tarifario institucional</t>
+          <t>$9.800.000 COP por semestre</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Descuento especial comunidad UniCafam / Afiliados Cafam</t>
+          <t>$7.840.000 COP por semestre (20% dcto para egresados)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Tarifa preferencial egresados UniCafam</t>
+          <t>$7.840.000 COP por semestre (20% dcto)</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Tarifa corporativa por volumen (&gt;3 inscritos)</t>
+          <t>$8.330.000 COP por semestre (15% dcto por convenios colectivos)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Cohortes semestrales continuas</t>
+          <t>Admisiones anuales para inicio en cada periodo académico del segundo semestre</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>El presente programa responde a las demandas urgentes del mercado laboral identificadas por el Observatorio de Inteligencia Laboral de UniCafam. El análisis de vacantes revela una brecha del sector productivo en competencias de Especialización en Ingeniería de Datos y Arquitecturas Cloud. El impacto salarial proyectado (Salarios proyectados de $10M - $18M COP en mercado local.) sustenta la pertinencia de formar talento especializado con alta tasa de empleabilidad y proyección nacional e internacional.</t>
+          <t>La ingeniería de datos es el pilar invisible pero más demandado del ecosistema de analítica moderno. Las ofertas para Ingenieros de Datos representan el 11.2% del total analizado, pero se caracterizan por una de las compensaciones promedio más elevadas del mercado nacional (salario promedio de $15M a $18M COP para especialistas en Azure, Databricks y Google Cloud). Un tecnólogo de UniCafam o un egresado de Ingeniería de Sistemas puede dar un salto profesional sin precedentes mediante este posgrado de un año. Mientras otros programas del mercado se centran excesivamente en la estadística teórica, UniCafam se posicionará como líder indiscutible en la formación de arquitectos de infraestructura, orquestación, Big Data distribuido y optimización de flujos de valor del dato empresarial, atendiendo una necesidad desatendida en el ecosistema nacional.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -2424,9 +2424,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Desarrollar competencias especializadas en Especialización en Ingeniería de Datos y Arquitecturas Cloud para responder a los desafíos tecnológicos del mercado.
-• Implementar soluciones técnicas reales mediante proyectos aplicados utilizando herramientas líderes de la industria.
-• Integrar metodologías ágiles y estándares internacionales en el ciclo de vida de los datos e inteligencia artificial.</t>
+          <t>• Objetivo General: Formar especialistas capaces de estructurar, optimizar y liderar la arquitectura de almacenamiento, procesamiento y distribución de flujos de datos empresariales multi-nube bajo estándares de seguridad y alta disponibilidad.
+• Objetivo Específico 1: Configurar sistemas distribuidos e infraestructuras híbridas que procesen petabytes de datos estructurados y no estructurados de manera eficiente.
+• Objetivo Específico 2: Diseñar flujos de integración y orquestación de datos automatizados robustos con tolerancia a fallas utilizando herramientas líderes como Apache Airflow.
+• Objetivo Específico 3: Implementar arquitecturas modernas de almacenamiento analítico como Lakehouses, Databricks y Delta Lakes.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -2470,7 +2471,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Tecnólogos o profesionales en áreas de sistemas, estadística o ingeniería con manejo de Python/SQL.</t>
+          <t>Egresados del pregrado profesional en Ciencia de Datos, ingenieros de sistemas, ingenieros de software, tecnólogos en análisis de datos de UniCafam con experiencia profesional comprobada en programación avanzada y bases de datos relacionales, y profesionales de carreras cuantitativas de TI.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -2505,7 +2506,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Metodología 100% teórico-práctica con enfoque en Aprendizaje Basado en Retos y Proyectos Reales (PBL). Las sesiones combinan fundamentación conceptual, laboratorios guiados en la nube y trabajo autónomo con acompañamiento de expertos de la industria. Cada módulo concluye con un entregable técnico aplicable.</t>
+          <t>La metodología pedagógica integra estudios de casos reales con prácticas de co-diseño de arquitectura empresarial en la nube. Los laboratorios se desarrollan utilizando arquitecturas multi-cloud. Cada módulo de posgrado requiere la resolución de un problema de rendimiento de big data empresarial, en el cual se evalúa no solo el funcionamiento lógico sino el costo computacional de la nube, preparando al estudiante para gestionar recursos de tecnología reales de forma eficiente.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -2549,10 +2550,9 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Alineación directa con los requisitos reales de vacantes analizadas en el Observatorio Laboral.
-✔ Enfoque en tecnologías de alta prima salarial (Salarios proyectados de $10M - $18M COP en mercado local.).
-✔ Certificación institucional respaldada por la Fundación Universitaria Cafam.
-✔ Docentes activos y líderes técnicos en empresas multinacionales de tecnología.</t>
+          <t>✔ Alineación directa con la ruta de certificación oficial de Microsoft Certified: Azure Data Engineer Associate y Databricks Certified Associate Developer.
+✔ Acceso preferente al Laboratorio de Ciberseguridad y Big Data de la Escuela de Ingeniería de UniCafam.
+✔ Cátedra abierta de casos de éxito dictada por Directores de Datos (CDOs) de corporaciones líderes en la región.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -2645,28 +2645,28 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Ingeniería de Pipelines de Datos a Escala</t>
+          <t>Procesamiento Distribuido a Gran Escala con Databricks &amp; Spark</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Unidades Temáticas:
-1. Fundamentación y Arquitectura.
-2. Implementación Práctica y Laboratorios (Apache Spark, PySpark, Airflow).
-3. Proyecto de Aplicación y Evaluación.
-Resultados de Aprendizaje:
-Implementar procesos de extracción, transformación y carga (ETL) utilizando frameworks de procesamiento distribuido. [Stack: Apache Spark, PySpark, Airflow]</t>
+          <t>1. Fundamentos de computación distribuida y arquitecturas de memoria RAM masiva.
+2. Arquitectura interna de Apache Spark y APIs principales (DataFrames y SQL).
+3. Gestión de clusters de datos, procesamiento Batch y Streaming de datos a gran escala.
+4. Introducción a la plataforma unificada Databricks.
+5. El paradigma Modern Lakehouse y persistencia tolerante con Delta Lake.
+6. Optimización de rendimiento de procesamiento distribuido y particionamiento de datos. [Stack: Apache Spark, PySpark, Databricks, Delta Lake, Parquet]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Módulo 1 - Semanas 1 a 4</t>
+          <t>Semanas 1 a 12 (Primer Semestre)</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>96 h</t>
+          <t>192 h</t>
         </is>
       </c>
     </row>
@@ -2688,63 +2688,89 @@
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
     </row>
-    <row r="42" ht="10" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1">
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>DOCENTES</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Nombre del Docente / Rol</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Módulo Asignado</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Perfil de Experto / Requisitos y Credenciales</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="n"/>
-      <c r="H43" s="13" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="17" t="inlineStr"/>
+      <c r="C42" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Orquestación de Pipelines &amp; Cloud Integration</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>1. Flujos lógicos e interdependencia de procesos de datos.
+2. Concepto de DAG (Directed Acyclic Graphs) y automatización.
+3. Implementación de orquestadores industriales: Apache Airflow profundo.
+4. Integración y despliegue continuo de DAGs en AWS y Azure.
+5. Monitoreo automatizado, alarmas integradas y control de fallas en producción.
+6. Gobierno, linaje y procedencia de datos en pipelines corporativos. [Stack: Apache Airflow, AWS, Azure, GitHub Enterprise, Datadog]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>Semanas 13 a 24 (Primer Semestre)</t>
+        </is>
+      </c>
+      <c r="H42" s="21" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
       <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Especialista / Magíster en Apache Spark</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Ingeniería de Pipelines de Datos a Escala</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Profesional con más de 5 años de experiencia liderando proyectos de Ingeniería de Pipelines de Datos a Escala en el sector productivo, con certificaciones internacionales en el stack tecnológico enseñado.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+      <c r="C45" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Infraestructura como Código, Docker &amp; Kubernetes para Datos</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>1. Virtualización a nivel de sistema operativo y concepto de contenedores.
+2. Creación y composición avanzada de redes locales y servicios multi-contenedor con Docker Compose.
+3. Fundamentos de orquestación a escala con Kubernetes.
+4. Despliegue de bases de datos y orquestadores en entornos clúster autocontrolados.
+5. Infraestructura como Código (IaC) utilizando Terraform para aprovisionamiento automatizado.
+6. Seguridad aplicada a redes de Big Data de alta disponibilidad. [Stack: Docker, Kubernetes, Terraform, Helm, YAML]</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>Semanas 1 a 12 (Segundo Semestre)</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
@@ -2753,52 +2779,206 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="10" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>DOCENTES</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Nombre del Docente / Rol</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Módulo Asignado</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Perfil de Experto / Requisitos y Credenciales</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="n"/>
+      <c r="H49" s="13" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
+      <c r="G50" s="13" t="n"/>
+      <c r="H50" s="13" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Especialista de Infraestructuras Big Data y Spark</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Procesamiento Distribuido a Gran Escala con Databricks &amp; Spark</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Ingeniero de Datos con posgrado en Big Data, maestría finalizada, con certificación oficial activa Databricks Certified Solutions Architect y experiencia de +6 años diseñando sistemas para multinacionales.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" s="17" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Arquitecto Senior de Integraciones Cloud</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>Orquestación de Pipelines &amp; Cloud Integration</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>Magíster en Ingeniería de Sistemas con sólida experiencia en orquestación de datos corporativos, con proyectos a escala en producción utilizando Apache Airflow y Kubernetes en los principales proveedores de nube.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Especialista en DevOps e Infraestructura como Código (IaC)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Infraestructura como Código, Docker &amp; Kubernetes para Datos</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Ingeniero de Software especialista, certificado en Terraform y Kubernetes (CKA), con un mínimo de 5 años liderando departamentos de infraestructura ágil y automatizada en corporaciones de telecomunicaciones o banca.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="65">
     <mergeCell ref="B22:B25"/>
-    <mergeCell ref="E43:E44"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C55:D56"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="E51:E52"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C26:H28"/>
+    <mergeCell ref="E42:F44"/>
+    <mergeCell ref="F49:H50"/>
     <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="C51:D52"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B45:B47"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="B26:B28"/>
+    <mergeCell ref="F53:H54"/>
     <mergeCell ref="C18:H21"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="G37:H37"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C53:D54"/>
     <mergeCell ref="B29:B32"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="C42:C44"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B1:E4"/>
     <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="F55:H56"/>
     <mergeCell ref="C29:H32"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C45:C47"/>
     <mergeCell ref="G39:G41"/>
-    <mergeCell ref="F45:H46"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="C22:H25"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="F51:H52"/>
+    <mergeCell ref="E45:F47"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D45:D47"/>
     <mergeCell ref="C33:H35"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="B39:B41"/>
     <mergeCell ref="H39:H41"/>
+    <mergeCell ref="H45:H47"/>
+    <mergeCell ref="B51:B52"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E53:E54"/>
     <mergeCell ref="E37:F37"/>
-    <mergeCell ref="F43:H44"/>
     <mergeCell ref="D14:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2811,7 +2991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H46"/>
+  <dimension ref="B1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2906,7 +3086,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>MAESTRÍA EN INTELIGENCIA ARTIFICIAL Y ANALÍTICA ESTRATÉGICA</t>
+          <t>MAESTRÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS ESTRATÉGICA</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -2923,7 +3103,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Maestría Aplicada (Posgrado) - Magíster en IA Aplicada</t>
+          <t>Maestría Aplicada (Posgrado / Maestría) - Magíster en Inteligencia Artificial y Ciencia de Datos Estratégica</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -2940,7 +3120,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Sábados de 8:00 a.m. a 1:00 p.m. / Sesiones sincrónicas</t>
+          <t>Jornada Nocturna y Concentrada en Fines de Semana (Híbrida)</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -2974,7 +3154,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Próximo inicio de cohorte académica</t>
+          <t>Agosto de 2025</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -2991,7 +3171,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Al completar el número total de horas del programa</t>
+          <t>Junio de 2027</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -3013,7 +3193,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Por definir según tarifario institucional</t>
+          <t>$12.500.000 COP por semestre</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -3030,7 +3210,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Descuento especial comunidad UniCafam / Afiliados Cafam</t>
+          <t>$10.000.000 COP por semestre (20% dcto egresados/docentes)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -3047,7 +3227,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Tarifa preferencial egresados UniCafam</t>
+          <t>$10.000.000 COP por semestre (20% dcto)</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -3064,7 +3244,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Tarifa corporativa por volumen (&gt;3 inscritos)</t>
+          <t>$10.625.000 COP por semestre (15% dcto corporativo)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -3080,7 +3260,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Cohortes semestrales continuas</t>
+          <t>Apertura anual para cada segundo semestre académico</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -3098,7 +3278,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>El presente programa responde a las demandas urgentes del mercado laboral identificadas por el Observatorio de Inteligencia Laboral de UniCafam. El análisis de vacantes revela una brecha del sector productivo en competencias de Maestría en Inteligencia Artificial y Analítica Estratégica. El impacto salarial proyectado (Acceso al mercado remoto internacional con promedios &gt; $30M COP.) sustenta la pertinencia de formar talento especializado con alta tasa de empleabilidad y proyección nacional e internacional.</t>
+          <t>La cúspide del mercado laboral analítico global está dominada por vacantes de Científicos de Datos y Machine Learning Engineers (conjuntamente representan el 78.1% de la demanda en el observatorio). Mientras las ofertas de entrada locales pagan sumas intermedias, las posiciones de dirección técnica y diseño de arquitecturas complejas de Inteligencia Artificial superan con creces los salarios promedio remotos de $32M COP, con techos salariales de hasta $68M COP. Esta maestría aplicada de UniCafam cubre el espacio estratégico de liderazgo técnico e investigación corporativa. Ofrece una continuación natural a los egresados del Profesional en Ciencia de Datos, permitiéndoles profundizar en Deep Learning avanzado (PyTorch/TensorFlow), toma de decisiones estratégicas bajo enfoques causales y gobernanza ética de IA. UniCafam se consolidará como el hub de formación avanzada del más alto nivel, articulando la academia con el mercado remoto internacional de máxima remuneración.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -3142,9 +3322,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Desarrollar competencias especializadas en Maestría en Inteligencia Artificial y Analítica Estratégica para responder a los desafíos tecnológicos del mercado.
-• Implementar soluciones técnicas reales mediante proyectos aplicados utilizando herramientas líderes de la industria.
-• Integrar metodologías ágiles y estándares internacionales en el ciclo de vida de los datos e inteligencia artificial.</t>
+          <t>• Objetivo General: Formar líderes y tomadores de decisiones estratégicas que posean el más alto dominio tecnológico para diseñar, auditar e implementar soluciones complejas basadas en Inteligencia Artificial que generen valor económico exponencial y resuelvan problemas estructurales de las industrias.
+• Objetivo Específico 1: Diseñar arquitecturas de aprendizaje profundo complejas optimizadas para procesamiento de imagen, voz, secuencias temporales y agentes autónomos utilizando librerías avanzadas.
+• Objetivo Específico 2: Implementar enfoques de inferencia causal y modelado analítico avanzado para estructurar políticas de negocio basadas en atribución científica rigurosa.
+• Objetivo Específico 3: Establecer marcos éticos de gobernanza de la IA asegurando la privacidad, transparencia y explicabilidad algorítmica corporativa.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -3188,7 +3369,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Profesionales con sólida base matemática, estadística y de programación.</t>
+          <t>Profesionales y directores con perfiles en Ciencia de Datos, Ingeniería de Sistemas, Estadística, Matemáticas o profesionales con experiencia en analítica cuantitativa que deseen liderar la transformación mediante inteligencia artificial y acceder a roles directivos globales.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -3223,7 +3404,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Metodología 100% teórico-práctica con enfoque en Aprendizaje Basado en Retos y Proyectos Reales (PBL). Las sesiones combinan fundamentación conceptual, laboratorios guiados en la nube y trabajo autónomo con acompañamiento de expertos de la industria. Cada módulo concluye con un entregable técnico aplicable.</t>
+          <t>Seminarios avanzados de investigación aplicada combinados con laboratorios computacionales de alto rendimiento (GPU clusters). Los estudiantes formularán un Proyecto de Grado de Aplicación Industrial que debe resolver de manera efectiva un problema analítico de alta complejidad técnica y viabilidad de mercado dentro de una empresa real. La maestría promueve activamente el desarrollo de publicaciones científicas y patentes de algoritmos.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -3267,10 +3448,9 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Alineación directa con los requisitos reales de vacantes analizadas en el Observatorio Laboral.
-✔ Enfoque en tecnologías de alta prima salarial (Acceso al mercado remoto internacional con promedios &gt; $30M COP.).
-✔ Certificación institucional respaldada por la Fundación Universitaria Cafam.
-✔ Docentes activos y líderes técnicos en empresas multinacionales de tecnología.</t>
+          <t>✔ Uso de clústeres de supercómputo equipados con GPUs NVIDIA corporativas de alto rendimiento para el entrenamiento de modelos de Deep Learning complejos.
+✔ Networking corporativo de alto nivel: interacción continua con presidentes de empresas, gerentes de analítica e investigadores de todo el continente.
+✔ Homologación automática de créditos para egresados de la Especialización de UniCafam, reduciendo drásticamente la inversión y el tiempo de estudio de la maestría.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -3363,28 +3543,28 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Deep Learning y Procesamiento de Lenguaje Natural (NLP/LLMs)</t>
+          <t>Modelado Avanzado de Aprendizaje Profundo &amp; Redes Neuronales</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Unidades Temáticas:
-1. Fundamentación y Arquitectura.
-2. Implementación Práctica y Laboratorios (PyTorch, Hugging Face, LangChain, TensorFlow).
-3. Proyecto de Aplicación y Evaluación.
-Resultados de Aprendizaje:
-Desarrollar aplicaciones basadas en modelos de lenguaje de gran escala y arquitecturas de redes neuronales profundas. [Stack: PyTorch, Hugging Face, LangChain, TensorFlow]</t>
+          <t>1. Introducción al entrenamiento por retropropagación y gradientes en redes profundas.
+2. Arquitecturas de visión artificial complejas (CNNs y Redes Generativas Adversarias - GANs).
+3. Redes recurrentes y procesamiento secuencial (LSTMs y GRUs).
+4. Mecanismos de atención y Transformers profundos.
+5. Modelos fundacionales e inferencia multimodal (Visión-Lenguaje).
+6. Entrenamiento eficiente de redes a escala y ajuste fino (Fine-Tuning) utilizando PyTorch. [Stack: PyTorch, TensorFlow, Keras, Hugging Face, Weights &amp; Biases]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Módulo 1 - Semanas 1 a 4</t>
+          <t>Semanas 1 a 12 (Primer Semestre)</t>
         </is>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>144 h</t>
+          <t>192 h</t>
         </is>
       </c>
     </row>
@@ -3406,63 +3586,88 @@
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
     </row>
-    <row r="42" ht="10" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1">
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>DOCENTES</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Nombre del Docente / Rol</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Módulo Asignado</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Perfil de Experto / Requisitos y Credenciales</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="n"/>
-      <c r="H43" s="13" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="13" t="n"/>
-      <c r="H44" s="13" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="17" t="inlineStr"/>
+      <c r="C42" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Inferencia Causal &amp; Modelamiento Decisional para Negocios</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>1. Limitaciones de la correlación de datos convencional frente a la causalidad de eventos.
+2. Teoría de Grafos Causal y el Cálculo Do (Pearl's Causal Framework).
+3. Métodos experimentales modernos y pruebas A/B de escala industrial.
+4. Métodos cuasi-experimentales en ciencias de datos (Diff-in-Diff, RDD, Propensity Score Matching).
+5. Modelado causal para atribución comercial y optimización de políticas de precios dinámicos.
+6. Herramientas de estimación de efectos causales con Python. [Stack: DoWhy, CausalML, EconML, Statsmodels]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>Semanas 1 a 12 (Segundo Semestre)</t>
+        </is>
+      </c>
+      <c r="H42" s="21" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
       <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Especialista / Magíster en PyTorch</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Deep Learning y Procesamiento de Lenguaje Natural (NLP/LLMs)</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Profesional con más de 5 años de experiencia liderando proyectos de Deep Learning y Procesamiento de Lenguaje Natural (NLP/LLMs) en el sector productivo, con certificaciones internacionales en el stack tecnológico enseñado.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+      <c r="C45" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Gobernanza de Datos, Ética en IA &amp; Algoritmos Explicables (XAI)</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>1. Sesgo algorítmico, equidad informática (Algorithmic Fairness) y discriminación por IA.
+2. Métodos de interpretación y explicación de modelos complejos de caja negra (SHAP, LIME).
+3. Cumplimiento normativo e internacional de privacidad de datos (GDPR, Ley de Inteligencia Artificial de la UE y normativas locales del MEN).
+4. Gobierno de datos y aseguramiento de la robustez frente a ataques adversarios de modelos.
+5. Marcos de auditoría ética y responsabilidad corporativa algorítmica. [Stack: SHAP, LIME, Fairlearn, Alibi, InterpretML]</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>Semanas 1 a 12 (Tercer Semestre)</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>192 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
@@ -3471,52 +3676,206 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="10" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>DOCENTES</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Nombre del Docente / Rol</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Módulo Asignado</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Perfil de Experto / Requisitos y Credenciales</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="n"/>
+      <c r="H49" s="13" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
+      <c r="G50" s="13" t="n"/>
+      <c r="H50" s="13" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Científico de Datos Senior con Doctorado en Ciencias de la Computación / Deep Learning</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Modelado Avanzado de Aprendizaje Profundo &amp; Redes Neuronales</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Ph.D. en Computación o IA con amplias publicaciones científicas indexadas Q1 o Q2 en aprendizaje automático, con amplia experiencia de modelado complejo con frameworks de cómputo en la nube a gran escala.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" s="17" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Especialista en Inferencia Causal y Econometría Analítica</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>Inferencia Causal &amp; Modelamiento Decisional para Negocios</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>Doctor en Economía Cuantitativa o Estadística Aplicada, con vasta trayectoria laboral en diseño de experimentos de alta precisión de comportamiento de consumo e inferencia para industrias digitales de primer nivel.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Experto en Regulación de Datos y XAI (Explainable AI)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Gobernanza de Datos, Ética en IA &amp; Algoritmos Explicables (XAI)</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Ph.D. o Magíster en Ética Aplicada, Derecho de TI o Ciencia de Datos, que haya liderado procesos de auditoría del comportamiento ético de algoritmos de decisión de otorgamiento de crédito o contratación en entidades de la Unión Europea o América Latina.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="65">
     <mergeCell ref="B22:B25"/>
-    <mergeCell ref="E43:E44"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C55:D56"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="E51:E52"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C26:H28"/>
+    <mergeCell ref="E42:F44"/>
+    <mergeCell ref="F49:H50"/>
     <mergeCell ref="B33:B35"/>
-    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="C51:D52"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
+    <mergeCell ref="B45:B47"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="B26:B28"/>
+    <mergeCell ref="F53:H54"/>
     <mergeCell ref="C18:H21"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="G37:H37"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C53:D54"/>
     <mergeCell ref="B29:B32"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="C42:C44"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B1:E4"/>
     <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="F55:H56"/>
     <mergeCell ref="C29:H32"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C45:C47"/>
     <mergeCell ref="G39:G41"/>
-    <mergeCell ref="F45:H46"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="C22:H25"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="F51:H52"/>
+    <mergeCell ref="E45:F47"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D45:D47"/>
     <mergeCell ref="C33:H35"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="B39:B41"/>
     <mergeCell ref="H39:H41"/>
+    <mergeCell ref="H45:H47"/>
+    <mergeCell ref="B51:B52"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E53:E54"/>
     <mergeCell ref="E37:F37"/>
-    <mergeCell ref="F43:H44"/>
     <mergeCell ref="D14:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/curriculo_unicafam/mig_propuestas/ofertas_academicas_mig_consolidado.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/ofertas_academicas_mig_consolidado.xlsx
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -200,6 +200,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -567,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H51"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -614,7 +617,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0 (APROBADO)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -631,7 +634,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -1305,11 +1308,81 @@
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
     </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="13" t="n"/>
+      <c r="D53" s="13" t="n"/>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="13" t="n"/>
+      <c r="G53" s="13" t="n"/>
+      <c r="H53" s="13" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>ESTADO DE APROBACIÓN</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>APROBADO (Versión v1)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>AVAL / DECISIÓN DIRECTIVA</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Dr. Carlos Alberto Gómez (Decano Escuela de Ingeniería y Tecnología)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>FECHA ÚLTIMA DECISIÓN</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:34:04</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="62">
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C54:H54"/>
+    <mergeCell ref="C55:H55"/>
     <mergeCell ref="C46:D47"/>
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
@@ -1322,12 +1395,14 @@
     <mergeCell ref="B46:B47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="F48:H49"/>
+    <mergeCell ref="C56:H56"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A54:B54"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="C48:D49"/>
     <mergeCell ref="C18:H21"/>
@@ -1337,11 +1412,13 @@
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="B29:B32"/>
     <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A56:B56"/>
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B1:E4"/>
     <mergeCell ref="B37:B38"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="C29:H32"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="G42:G44"/>
@@ -1356,6 +1433,7 @@
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="B39:B41"/>
     <mergeCell ref="H39:H41"/>
+    <mergeCell ref="A53:H53"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="C50:D51"/>
@@ -1373,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H46"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1420,7 +1498,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -1437,7 +1515,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -2035,23 +2113,96 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n"/>
+      <c r="C48" s="13" t="n"/>
+      <c r="D48" s="13" t="n"/>
+      <c r="E48" s="13" t="n"/>
+      <c r="F48" s="13" t="n"/>
+      <c r="G48" s="13" t="n"/>
+      <c r="H48" s="13" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>ESTADO DE APROBACIÓN</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>PENDIENTE_REVISION (Versión v1)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>AVAL / DECISIÓN DIRECTIVA</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente de Visto Bueno por Comité Curricular</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>FECHA ÚLTIMA DECISIÓN</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>En proceso de revisión</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="52">
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="A49:B49"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C26:H28"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="C43:D44"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C51:H51"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="B26:B28"/>
@@ -2064,11 +2215,13 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B1:E4"/>
     <mergeCell ref="B37:B38"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="C29:H32"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="F45:H46"/>
     <mergeCell ref="C22:H25"/>
     <mergeCell ref="E45:E46"/>
+    <mergeCell ref="C49:H49"/>
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="C6:H6"/>
@@ -2093,7 +2246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H56"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2140,7 +2293,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0 (APROBADO)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -2157,7 +2310,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -2913,8 +3066,76 @@
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="13" t="n"/>
+      <c r="H58" s="13" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>ESTADO DE APROBACIÓN</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>APROBADO (Versión v1)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>AVAL / DECISIÓN DIRECTIVA</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Ing. María Fernanda Rojas (Directora de Programa Ciencia de Datos)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>FECHA ÚLTIMA DECISIÓN</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:34:04</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="72">
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
@@ -2923,6 +3144,7 @@
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="E55:E56"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
@@ -2932,16 +3154,20 @@
     <mergeCell ref="F49:H50"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C59:H59"/>
     <mergeCell ref="C51:D52"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C60:H60"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="F53:H54"/>
     <mergeCell ref="C18:H21"/>
     <mergeCell ref="D13:H13"/>
+    <mergeCell ref="C61:H61"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="H42:H44"/>
     <mergeCell ref="C8:H8"/>
@@ -2980,6 +3206,8 @@
     <mergeCell ref="E53:E54"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="D14:H14"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2991,7 +3219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H56"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3038,7 +3266,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -3055,7 +3283,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -3810,8 +4038,76 @@
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="13" t="n"/>
+      <c r="H58" s="13" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>ESTADO DE APROBACIÓN</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>PENDIENTE_REVISION (Versión v1)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>AVAL / DECISIÓN DIRECTIVA</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente de Visto Bueno por Comité Curricular</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>FECHA ÚLTIMA DECISIÓN</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>En proceso de revisión</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="72">
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
@@ -3820,6 +4116,7 @@
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="E55:E56"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
@@ -3829,16 +4126,20 @@
     <mergeCell ref="F49:H50"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C59:H59"/>
     <mergeCell ref="C51:D52"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C60:H60"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="F53:H54"/>
     <mergeCell ref="C18:H21"/>
     <mergeCell ref="D13:H13"/>
+    <mergeCell ref="C61:H61"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="H42:H44"/>
     <mergeCell ref="C8:H8"/>
@@ -3877,6 +4178,8 @@
     <mergeCell ref="E53:E54"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="D14:H14"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/curriculo_unicafam/mig_propuestas/ofertas_academicas_mig_consolidado.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/ofertas_academicas_mig_consolidado.xlsx
@@ -7,10 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PROP_01_Electiva de Pro" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PROP_02_Microcredencial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PROP_03_Especialización" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PROP_04_Maestría Aplica" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PROP_02_Microcredencial" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PROP_03_Especialización" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -186,6 +184,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -200,9 +201,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -570,887 +568,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MATRIZ INTEGRADA DE GESTION MIG
-OFERTA Y DISEÑO CURRICULAR ACADÉMICO</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Código:</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>MIDOFO05</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Versión:</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>1.0 (APROBADO)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Fecha:</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Página:</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="10" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>NOMBRE DEL PROGRAMA</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>IMPLEMENTACIÓN DE ARQUITECTURAS CLOUD Y MLOPS</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>TIPO / NIVEL</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Electiva de Profundización (Pregrado) - Certificado de Profundización en Cloud Data Engineering &amp; MLOps</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>HORARIO</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Sábados de 7:00 a.m. a 1:00 p.m. / Sesiones sincrónicas virtuales y laboratorios presenciales bimensuales</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>DURACIÓN</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>1 semestre | 6 Créditos (288 Horas totales)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>FECHA DE INICIO</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Febrero de 2025</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>FECHA DE TERMINACIÓN</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Junio de 2025</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>INVERSIÓN</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Público externo</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>$2.950.000 COP</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Comunidad UniCafam</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>$2.212.500 COP (25% dcto afiliados/estudiantes)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>$2.360.000 COP (20% dcto)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Grupos / Empresas</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>$2.065.000 COP (por convenio empresarial &gt;3 personas)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>PRÓXIMAS EDICIONES</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Cohortes en el primer y segundo semestre de cada año académico</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="8" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>JUSTIFICACIÓN</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>La tecnología en Análisis y Gestión de Datos de UniCafam forma tecnólogos con excelente dominio de análisis predictivo, Python y SQL. Sin embargo, para acceder a vacantes de alta remuneración, estos profesionales deben operar en la nube y automatizar el ciclo de vida de los modelos. Según el observatorio, AWS y GCP registran un porcentaje de penetración conjunto de más del 32% en la demanda y salarios de hasta $15M COP. Introducir una electiva de 6 créditos en el último año de la tecnología y articulación profesional asegura que el estudiante no solo construya modelos (lo que ya hace muy bien), sino que aprenda a empaquetarlos, desplegarlos y monitorearlos. Esto duplica de inmediato el espectro de empleabilidad hacia roles de Junior Cloud Engineer y MLOps Practitioner, apalancando la prima salarial internacional.</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>OBJETIVOS</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>• Objetivo General: Desarrollar competencias teórico-prácticas en la estructuración de flujos de datos automatizados y despliegue continuo de modelos de Machine Learning en entornos de computación en la nube empresariales.
-• Objetivo Específico 1: Implementar arquitecturas de almacenamiento y procesamiento serverless en AWS y GCP para canalizar volúmenes de datos a escala.
-• Objetivo Específico 2: Contenedorizar aplicaciones de IA utilizando Docker y desplegar microservicios eficientes accesibles a través de APIs web.
-• Objetivo Específico 3: Diseñar ciclos de vida automatizados de modelos (MLOps) integrando herramientas de tracking como MLflow y pipelines básicos de CI/CD.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>DIRIGIDO A</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Estudiantes de 5to semestre de la Tecnología en Análisis y Gestión de Datos, estudiantes de Ingeniería de Sistemas de UniCafam y egresados tecnólogos de datos que dominen Python intermedio y bases de datos relacionales.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>METODOLOGÍA</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Modelo pedagógico activo basado en retos (PBL - Project Based Learning). Los estudiantes desarrollarán un proyecto integrador a lo largo del semestre consistente en tomar un modelo predictivo previamente entrenado en su carrera, empaquetarlo en un contenedor Docker, desplegarlo como microservicio en AWS, y configurar su respectivo pipeline de control, monitoreo y CI/CD utilizando GitHub Actions y MLflow. Las clases constan de un 30% de conceptualización y un 70% de talleres aplicados en laboratorios cloud (AWS Academy y Google Cloud for Education).</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>VALOR(ES) AGREGADO(S)</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>✔ Acceso gratuito a entornos sandbox de AWS y Google Cloud a través de convenios educativos de UniCafam.
-✔ Voucher de descuento de hasta el 50% para la certificación oficial AWS Certified Cloud Practitioner o GCP Associate Cloud Engineer.
-✔ Desarrollo de un portafolio de producción alojado en GitHub listo para ser presentado en procesos de selección internacional.</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-    </row>
-    <row r="36" ht="10" customHeight="1"/>
-    <row r="37" ht="20" customHeight="1">
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>PROGRAMA ACADÉMICO</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Contenido</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>Cronograma de clases</t>
-        </is>
-      </c>
-      <c r="H37" s="13" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Módulo</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>Módulo</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Módulo / Temáticas y Stack</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>Fecha / Semanas</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>No. Horas</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Cloud Data Engineering (AWS &amp; GCP Foundations)</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>1. Fundamentos de nube e Infraestructura Global.
-2. Almacenamiento de datos escalable en AWS (S3) y GCP (Cloud Storage).
-3. Bases de datos modernas y Data Warehousing (Amazon Redshift, Google BigQuery).
-4. Orquestación serverless y ETL en la nube (AWS Glue, Cloud Dataflow).
-5. Seguridad, gobernanza de datos y manejo de accesos (IAM). [Stack: AWS S3, Google Cloud Storage, BigQuery, AWS Glue, IAM]</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>Semanas 1 a 8</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>144 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="17" t="inlineStr"/>
-      <c r="C42" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>MLOps &amp; Despliegue de Modelos de IA</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>1. Introducción al ciclo de vida de MLOps y comparación con DevOps.
-2. Creación de APIs web para consumo de modelos (FastAPI, Flask).
-3. Contenedorización de aplicaciones y entornos aislados de desarrollo con Docker.
-4. Tracking de experimentos, almacenamiento de artefactos y registro de modelos con MLflow.
-5. Monitoreo básico del comportamiento del modelo en producción (Data Drift e inferencia). [Stack: Docker, FastAPI, MLflow, GitHub Actions]</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>Semanas 9 a 16</t>
-        </is>
-      </c>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t>144 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-    </row>
-    <row r="45" ht="10" customHeight="1"/>
-    <row r="46" ht="20" customHeight="1">
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>DOCENTES</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Nombre del Docente / Rol</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>Módulo Asignado</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Perfil de Experto / Requisitos y Credenciales</t>
-        </is>
-      </c>
-      <c r="G46" s="13" t="n"/>
-      <c r="H46" s="13" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
-      <c r="F47" s="13" t="n"/>
-      <c r="G47" s="13" t="n"/>
-      <c r="H47" s="13" t="n"/>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Especialista en Infraestructura de Datos Cloud</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>Cloud Data Engineering (AWS &amp; GCP Foundations)</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>Ingeniero de Sistemas o de Datos con especialización o maestría en áreas afines, certificado oficialmente como AWS Certified Solutions Architect o GCP Professional Cloud Architect, con experiencia laboral mínima de 4 años en el sector corporativo diseñando pipelines en la nube.</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="n"/>
-    </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="B50" s="17" t="inlineStr"/>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Ingeniero de Plataformas AI / MLOps Lead</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="22" t="inlineStr">
-        <is>
-          <t>MLOps &amp; Despliegue de Modelos de IA</t>
-        </is>
-      </c>
-      <c r="F50" s="19" t="inlineStr">
-        <is>
-          <t>Científico de Datos Senior o MLOps Engineer con experiencia laboral de más de 5 años en despliegue de modelos a gran escala, dominio experto en metodologías ágiles de ingeniería de software, empaquetamiento con Docker y orquestadores.</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="n"/>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-      <c r="G53" s="13" t="n"/>
-      <c r="H53" s="13" t="n"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="23" t="inlineStr">
-        <is>
-          <t>ESTADO DE APROBACIÓN</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>APROBADO (Versión v1)</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="23" t="inlineStr">
-        <is>
-          <t>AVAL / DECISIÓN DIRECTIVA</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Dr. Carlos Alberto Gómez (Decano Escuela de Ingeniería y Tecnología)</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="23" t="inlineStr">
-        <is>
-          <t>FECHA ÚLTIMA DECISIÓN</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-16 17:34:04</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C54:H54"/>
-    <mergeCell ref="C55:H55"/>
-    <mergeCell ref="C46:D47"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C26:H28"/>
-    <mergeCell ref="E42:F44"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="F48:H49"/>
-    <mergeCell ref="C56:H56"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:F41"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C48:D49"/>
-    <mergeCell ref="C18:H21"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B1:E4"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="C29:H32"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="C22:H25"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="F50:H51"/>
-    <mergeCell ref="C33:H35"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="F46:H47"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1498,7 +615,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0 (PENDIENTE_REVISION)</t>
+          <t>2.0 (APROBADO)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -1515,7 +632,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -1738,7 +855,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>La revolución de la Inteligencia Artificial Generativa y los Modelos de Lenguaje de Gran Escala (LLMs) ha transformado la demanda empresarial. Los egresados de UniCafam cuentan con sólidas competencias en Procesamiento de Lenguaje Natural (NLP) tradicional gracias a la materia 'Procesamiento de Texto y Técnicas de Información'. Esta microcredencial tiende un puente directo hacia las tecnologías más modernas de IA de Frontera: Retrieval-Augmented Generation (RAG) y bases de datos vectoriales. Conectando lo que ya saben de procesamiento de texto con LLMs comerciales y de código abierto (Llama, OpenAI, Claude), el egresado se transforma en un desarrollador de soluciones cognitivas inteligentes que automatizan la búsqueda de información corporativa, impulsando su empleabilidad en un mercado que valora estas competencias en niveles sumamente altos.</t>
+          <t>La revolución de la Inteligencia Artificial Generativa y los Modelos de Lenguaje de Gran Escala (LLMs) está redefiniendo la eficiencia operativa, la automatización del conocimiento y el ROI empresarial. Los profesionales deben trascender el desarrollo conceptual para entregar soluciones de alto valor corporativo orientadas al negocio. Esta microcredencial articula las competencias previas en NLP y análisis de datos de los egresados de UniCafam con arquitecturas de frontera como Retrieval-Augmented Generation (RAG), almacenamiento en bases de datos vectoriales y orquestación cognitiva. El programa enfatiza el caso de negocio real, el cálculo de costo-beneficio de inferencias y la entrega de un producto funcional desplegado en producción cloud (AWS/Azure) y respaldado en GitHub, otorgando una ventaja altamente competitiva y demostrable en entrevistas de trabajo e iniciativas de transformación digital.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -1782,10 +899,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Objetivo General: Capacitar en el diseño, desarrollo e integración de sistemas de IA Generativa empresariales utilizando arquitecturas RAG para optimizar la toma de decisiones y la automatización de procesos de consulta.
-• Objetivo Específico 1: Utilizar frameworks avanzados de desarrollo (LangChain e Indexadores) para orquestar flujos cognitivos complejos basados en LLMs.
-• Objetivo Específico 2: Implementar bases de datos vectoriales para el almacenamiento de embeddings semánticos optimizados.
-• Objetivo Específico 3: Diseñar aplicaciones web que utilicen técnicas de Prompt Engineering avanzado y agentes inteligentes autónomos.</t>
+          <t>• Objetivo General: Capacitar en el diseño, desarrollo, evaluación de impacto financiero e integración de sistemas de IA Generativa empresariales utilizando arquitecturas RAG para optimizar la toma de decisiones, garantizando el despliegue funcional en entornos de nube y repositorios públicos orientados a portafolios profesionales.
+• Objetivo Específico 1: Evaluar casos de uso de negocio y modelos de orquestación cognitiva (LangChain / LlamaIndex) para resolver ineficiencias operativas con métricas claras de ROI.
+• Objetivo Específico 2: Implementar bases de datos vectoriales en producción para el almacenamiento y recuperación de embeddings semánticos con enfoque en seguridad y costo eficientes.
+• Objetivo Específico 3: Desplegar un Proyecto Integrador de negocio en un servicio de nube pública (AWS o Azure) con código fuente versionado en GitHub para demostración efectiva en procesos de selección y desarrollo profesional.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -1829,7 +946,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Científicos de datos, tecnólogos en análisis de datos, ingenieros de desarrollo de software, analistas de BI senior y entusiastas de la tecnología con nociones lógicas de programación en Python.</t>
+          <t>Científicos de datos, tecnólogos en análisis de datos, ingenieros de desarrollo de software, analistas de BI senior, consultores de innovación y líderes técnicos con nociones lógicas de programación en Python interesados en aplicar IA con impacto real en los negocios.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -1864,7 +981,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Enfoque de taller práctico hands-on. Cada sesión sincrónica introduce un reto técnico real de la industria (p. ej., construir un chatbot que responda preguntas basadas exclusivamente en los manuales de procedimientos de una empresa). Los laboratorios se desarrollan sobre cuadernos de Jupyter de Google Colab utilizando APIs comerciales y modelos open-source de Hugging Face. Se utiliza un canal continuo de comunicación en Discord para mentorías personalizadas de código.</t>
+          <t>Enfoque 100% práctico ('learning-by-doing') orientado a la resolución de retos de negocio. A lo largo del programa, los participantes desarrollan un Proyecto Integrador de IA Generativa basado en una necesidad empresarial real (ej. asistente financiero de consulta documental, automatizador RAG para áreas normativas o gestor inteligente de servicio al cliente). Las sesiones combinan teoría aplicada, laboratorios en Google Colab con APIs comerciales y modelos open-source, y mentorías dedicadas al versionamiento de código en GitHub y el despliegue continuo en la nube (AWS/Azure). El programa finaliza con un Demo Day donde los estudiantes presentan sus productos desplegados en producción y sus repositorios públicos para exhibir en su portafolio laboral.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1908,9 +1025,11 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Inclusión en el portafolio institucional de microcredenciales digitales insignias de UniCafam con estándar internacional OpenBadges para compartir en LinkedIn.
-✔ Acceso directo a la comunidad de expertos en Inteligencia Artificial de la escuela de Ingeniería UniCafam.
-✔ Plantillas de código listas para producción en entornos empresariales.</t>
+          <t>✔ Proyecto Final integrador real desplegado en infraestructura Cloud (AWS/Azure) y listo para incluir en el perfil de LinkedIn y portafolio laboral.
+✔ Repositorio funcional en GitHub estructurado bajo estándares de la industria, optimizado para ser presentado como evidencia técnica en entrevistas de trabajo.
+✔ Inclusión en el portafolio institucional de microcredenciales digitales insignias de UniCafam con estándar internacional OpenBadges.
+✔ Acceso directo a la comunidad de expertos en Inteligencia Artificial y Transformación Digital de la Escuela de Ingeniería de UniCafam.
+✔ Plantillas de código y arquitectura orientadas a producción empresarial con estimación de costos operacionales.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -2003,19 +1122,19 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales</t>
+          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales para Soluciones de Negocio</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>1. Introducción a la IA Generativa, Modelos Fundacionales y Transformers.
-2. Fundamentos de Embeddings: Conversión de texto a vectores densos.
-3. Bases de Datos Vectoriales: Almacenamiento, indexación y búsqueda en Pinecone, ChromaDB y Qdrant.
-4. El flujo RAG (Retrieval-Augmented Generation): Conexión de documentos privados con LLMs.
-5. Frameworks de Orquestación: Construcción paso a paso con LangChain y LlamaIndex.
-6. Prompt Engineering Avanzado, técnicas Few-Shot y control de alucinaciones.
-7. Agentes autónomos de IA que interactúan con APIs externas y SQL corporativo.
-8. Despliegue de un prototipo interactivo utilizando Streamlit. [Stack: LangChain, Pinecone, ChromaDB, OpenAI API, Hugging Face, Streamlit]</t>
+          <t>1. Estrategia de IA Generativa en Negocios: Casos de uso, estimación de ROI, latencia y costos de inferencia por token.
+2. Fundamentos de Embeddings &amp; Búsqueda Semántica aplicados a repositorios documentales corporativos.
+3. Bases de Datos Vectoriales (Pinecone, ChromaDB, Qdrant): Gestión, indexación, particionamiento por tenant y seguridad de datos empresariales.
+4. Flujo RAG (Retrieval-Augmented Generation) Avanzado: Chunking estratégico, re-ranking y reducción de alucinaciones en entornos de negocio.
+5. Frameworks de Orquestación: Construcción paso a paso de flujos cognitivos eficientes con LangChain y LlamaIndex.
+6. Agentes Autónomos y Tool Use: Integración con APIs corporativas y bases de datos SQL para analítica conversacional.
+7. Versionamiento Profesional: Estructuración de proyectos, buenas prácticas de código y documentación en GitHub para portafolio laboral.
+8. Proyecto Final Integrador &amp; Despliegue Cloud: Empaquetamiento de la aplicación (Streamlit/FastAPI) y despliegue continuo en AWS (App Runner/EC2) o Azure (Container Apps/Web Apps) con demostración para entrevistas de trabajo. [Stack: LangChain, LlamaIndex, Pinecone, ChromaDB, OpenAI API / Claude, GitHub, AWS (App Runner / EC2), Azure (Container Apps), Streamlit / FastAPI]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
@@ -2087,18 +1206,18 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Investigador / Ingeniero Senior en NLP &amp; IA Generativa</t>
+          <t>Investigador / Ingeniero Senior en NLP &amp; IA Generativa para Negocios</t>
         </is>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales</t>
+          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales para Soluciones de Negocio</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Profesional en Ingeniería de Sistemas, Inteligencia Artificial o Ciencia de Datos, con Maestría o Doctorado en Inteligencia Artificial o Computación Cognitiva, con publicaciones científicas o experiencia de mínimo 3 años desarrollando productos basados en tecnologías Transformers y modelos GPT.</t>
+          <t>Profesional en Ingeniería de Sistemas, Inteligencia Artificial o Ciencia de Datos, con Maestría o Doctorado en IA, Ciencias de la Computación o Áreas Afines, con más de 3 años de experiencia liderando proyectos de IA Generativa en la industria, despliegue en entornos Cloud (AWS/Azure) y desarrollo de soluciones de impacto de negocio.</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -2128,7 +1247,7 @@
       <c r="H48" s="13" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>ESTADO DE APROBACIÓN</t>
         </is>
@@ -2136,7 +1255,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>PENDIENTE_REVISION (Versión v1)</t>
+          <t>APROBADO (Versión v2)</t>
         </is>
       </c>
       <c r="D49" s="2" t="n"/>
@@ -2146,7 +1265,7 @@
       <c r="H49" s="2" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>AVAL / DECISIÓN DIRECTIVA</t>
         </is>
@@ -2154,7 +1273,7 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Pendiente de Visto Bueno por Comité Curricular</t>
+          <t>Decanatura / Comité Curricular UniCafam (Usuario Aprobador)</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
@@ -2164,7 +1283,7 @@
       <c r="H50" s="2" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="23" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>FECHA ÚLTIMA DECISIÓN</t>
         </is>
@@ -2172,7 +1291,7 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>En proceso de revisión</t>
+          <t>2026-10-24 08:59:15</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>
@@ -2240,7 +1359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2842,8 +1961,8 @@
       <c r="H41" s="2" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="17" t="inlineStr"/>
-      <c r="C42" s="18" t="n">
+      <c r="B42" s="18" t="inlineStr"/>
+      <c r="C42" s="19" t="n">
         <v>2</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -2851,7 +1970,7 @@
           <t>Orquestación de Pipelines &amp; Cloud Integration</t>
         </is>
       </c>
-      <c r="E42" s="19" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>1. Flujos lógicos e interdependencia de procesos de datos.
 2. Concepto de DAG (Directed Acyclic Graphs) y automatización.
@@ -2862,12 +1981,12 @@
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
-      <c r="G42" s="20" t="inlineStr">
+      <c r="G42" s="21" t="inlineStr">
         <is>
           <t>Semanas 13 a 24 (Primer Semestre)</t>
         </is>
       </c>
-      <c r="H42" s="21" t="inlineStr">
+      <c r="H42" s="22" t="inlineStr">
         <is>
           <t>192 h</t>
         </is>
@@ -3007,19 +2126,19 @@
       <c r="H52" s="2" t="n"/>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="B53" s="17" t="inlineStr"/>
+      <c r="B53" s="18" t="inlineStr"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Arquitecto Senior de Integraciones Cloud</t>
         </is>
       </c>
       <c r="D53" s="2" t="n"/>
-      <c r="E53" s="22" t="inlineStr">
+      <c r="E53" s="23" t="inlineStr">
         <is>
           <t>Orquestación de Pipelines &amp; Cloud Integration</t>
         </is>
       </c>
-      <c r="F53" s="19" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
         <is>
           <t>Magíster en Ingeniería de Sistemas con sólida experiencia en orquestación de datos corporativos, con proyectos a escala en producción utilizando Apache Airflow y Kubernetes en los principales proveedores de nube.</t>
         </is>
@@ -3081,7 +2200,7 @@
       <c r="H58" s="13" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="23" t="inlineStr">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>ESTADO DE APROBACIÓN</t>
         </is>
@@ -3099,7 +2218,7 @@
       <c r="H59" s="2" t="n"/>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>AVAL / DECISIÓN DIRECTIVA</t>
         </is>
@@ -3117,7 +2236,7 @@
       <c r="H60" s="2" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="23" t="inlineStr">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>FECHA ÚLTIMA DECISIÓN</t>
         </is>
@@ -3126,978 +2245,6 @@
       <c r="C61" s="7" t="inlineStr">
         <is>
           <t>2026-10-16 17:34:04</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C55:D56"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C26:H28"/>
-    <mergeCell ref="E42:F44"/>
-    <mergeCell ref="F49:H50"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="C59:H59"/>
-    <mergeCell ref="C51:D52"/>
-    <mergeCell ref="E39:F41"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C60:H60"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="F53:H54"/>
-    <mergeCell ref="C18:H21"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="H42:H44"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C53:D54"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B1:E4"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="F55:H56"/>
-    <mergeCell ref="C29:H32"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="C22:H25"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="F51:H52"/>
-    <mergeCell ref="E45:F47"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="C33:H35"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="H45:H47"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A58:H58"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>MATRIZ INTEGRADA DE GESTION MIG
-OFERTA Y DISEÑO CURRICULAR ACADÉMICO</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Código:</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>MIDOFO05</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Versión:</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>1.0 (PENDIENTE_REVISION)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Fecha:</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Página:</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="10" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>NOMBRE DEL PROGRAMA</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>MAESTRÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS ESTRATÉGICA</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>TIPO / NIVEL</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Maestría Aplicada (Posgrado / Maestría) - Magíster en Inteligencia Artificial y Ciencia de Datos Estratégica</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>HORARIO</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Jornada Nocturna y Concentrada en Fines de Semana (Híbrida)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>DURACIÓN</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>4 semestres | 48 Créditos (2304 Horas totales)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>FECHA DE INICIO</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Agosto de 2025</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>FECHA DE TERMINACIÓN</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Junio de 2027</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>INVERSIÓN</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Público externo</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>$12.500.000 COP por semestre</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Comunidad UniCafam</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>$10.000.000 COP por semestre (20% dcto egresados/docentes)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>$10.000.000 COP por semestre (20% dcto)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Grupos / Empresas</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>$10.625.000 COP por semestre (15% dcto corporativo)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>PRÓXIMAS EDICIONES</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Apertura anual para cada segundo semestre académico</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="8" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>JUSTIFICACIÓN</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>La cúspide del mercado laboral analítico global está dominada por vacantes de Científicos de Datos y Machine Learning Engineers (conjuntamente representan el 78.1% de la demanda en el observatorio). Mientras las ofertas de entrada locales pagan sumas intermedias, las posiciones de dirección técnica y diseño de arquitecturas complejas de Inteligencia Artificial superan con creces los salarios promedio remotos de $32M COP, con techos salariales de hasta $68M COP. Esta maestría aplicada de UniCafam cubre el espacio estratégico de liderazgo técnico e investigación corporativa. Ofrece una continuación natural a los egresados del Profesional en Ciencia de Datos, permitiéndoles profundizar en Deep Learning avanzado (PyTorch/TensorFlow), toma de decisiones estratégicas bajo enfoques causales y gobernanza ética de IA. UniCafam se consolidará como el hub de formación avanzada del más alto nivel, articulando la academia con el mercado remoto internacional de máxima remuneración.</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>OBJETIVOS</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>• Objetivo General: Formar líderes y tomadores de decisiones estratégicas que posean el más alto dominio tecnológico para diseñar, auditar e implementar soluciones complejas basadas en Inteligencia Artificial que generen valor económico exponencial y resuelvan problemas estructurales de las industrias.
-• Objetivo Específico 1: Diseñar arquitecturas de aprendizaje profundo complejas optimizadas para procesamiento de imagen, voz, secuencias temporales y agentes autónomos utilizando librerías avanzadas.
-• Objetivo Específico 2: Implementar enfoques de inferencia causal y modelado analítico avanzado para estructurar políticas de negocio basadas en atribución científica rigurosa.
-• Objetivo Específico 3: Establecer marcos éticos de gobernanza de la IA asegurando la privacidad, transparencia y explicabilidad algorítmica corporativa.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>DIRIGIDO A</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Profesionales y directores con perfiles en Ciencia de Datos, Ingeniería de Sistemas, Estadística, Matemáticas o profesionales con experiencia en analítica cuantitativa que deseen liderar la transformación mediante inteligencia artificial y acceder a roles directivos globales.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>METODOLOGÍA</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Seminarios avanzados de investigación aplicada combinados con laboratorios computacionales de alto rendimiento (GPU clusters). Los estudiantes formularán un Proyecto de Grado de Aplicación Industrial que debe resolver de manera efectiva un problema analítico de alta complejidad técnica y viabilidad de mercado dentro de una empresa real. La maestría promueve activamente el desarrollo de publicaciones científicas y patentes de algoritmos.</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>VALOR(ES) AGREGADO(S)</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>✔ Uso de clústeres de supercómputo equipados con GPUs NVIDIA corporativas de alto rendimiento para el entrenamiento de modelos de Deep Learning complejos.
-✔ Networking corporativo de alto nivel: interacción continua con presidentes de empresas, gerentes de analítica e investigadores de todo el continente.
-✔ Homologación automática de créditos para egresados de la Especialización de UniCafam, reduciendo drásticamente la inversión y el tiempo de estudio de la maestría.</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-    </row>
-    <row r="36" ht="10" customHeight="1"/>
-    <row r="37" ht="20" customHeight="1">
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>PROGRAMA ACADÉMICO</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Contenido</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>Cronograma de clases</t>
-        </is>
-      </c>
-      <c r="H37" s="13" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Módulo</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>Módulo</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Módulo / Temáticas y Stack</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>Fecha / Semanas</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>No. Horas</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Modelado Avanzado de Aprendizaje Profundo &amp; Redes Neuronales</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>1. Introducción al entrenamiento por retropropagación y gradientes en redes profundas.
-2. Arquitecturas de visión artificial complejas (CNNs y Redes Generativas Adversarias - GANs).
-3. Redes recurrentes y procesamiento secuencial (LSTMs y GRUs).
-4. Mecanismos de atención y Transformers profundos.
-5. Modelos fundacionales e inferencia multimodal (Visión-Lenguaje).
-6. Entrenamiento eficiente de redes a escala y ajuste fino (Fine-Tuning) utilizando PyTorch. [Stack: PyTorch, TensorFlow, Keras, Hugging Face, Weights &amp; Biases]</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>Semanas 1 a 12 (Primer Semestre)</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>192 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="17" t="inlineStr"/>
-      <c r="C42" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>Inferencia Causal &amp; Modelamiento Decisional para Negocios</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>1. Limitaciones de la correlación de datos convencional frente a la causalidad de eventos.
-2. Teoría de Grafos Causal y el Cálculo Do (Pearl's Causal Framework).
-3. Métodos experimentales modernos y pruebas A/B de escala industrial.
-4. Métodos cuasi-experimentales en ciencias de datos (Diff-in-Diff, RDD, Propensity Score Matching).
-5. Modelado causal para atribución comercial y optimización de políticas de precios dinámicos.
-6. Herramientas de estimación de efectos causales con Python. [Stack: DoWhy, CausalML, EconML, Statsmodels]</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>Semanas 1 a 12 (Segundo Semestre)</t>
-        </is>
-      </c>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t>192 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Gobernanza de Datos, Ética en IA &amp; Algoritmos Explicables (XAI)</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>1. Sesgo algorítmico, equidad informática (Algorithmic Fairness) y discriminación por IA.
-2. Métodos de interpretación y explicación de modelos complejos de caja negra (SHAP, LIME).
-3. Cumplimiento normativo e internacional de privacidad de datos (GDPR, Ley de Inteligencia Artificial de la UE y normativas locales del MEN).
-4. Gobierno de datos y aseguramiento de la robustez frente a ataques adversarios de modelos.
-5. Marcos de auditoría ética y responsabilidad corporativa algorítmica. [Stack: SHAP, LIME, Fairlearn, Alibi, InterpretML]</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>Semanas 1 a 12 (Tercer Semestre)</t>
-        </is>
-      </c>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>192 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="10" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1">
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>DOCENTES</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>Nombre del Docente / Rol</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>Módulo Asignado</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Perfil de Experto / Requisitos y Credenciales</t>
-        </is>
-      </c>
-      <c r="G49" s="13" t="n"/>
-      <c r="H49" s="13" t="n"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="B50" s="13" t="n"/>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
-      <c r="H50" s="13" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Científico de Datos Senior con Doctorado en Ciencias de la Computación / Deep Learning</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>Modelado Avanzado de Aprendizaje Profundo &amp; Redes Neuronales</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>Ph.D. en Computación o IA con amplias publicaciones científicas indexadas Q1 o Q2 en aprendizaje automático, con amplia experiencia de modelado complejo con frameworks de cómputo en la nube a gran escala.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="B53" s="17" t="inlineStr"/>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>Especialista en Inferencia Causal y Econometría Analítica</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="22" t="inlineStr">
-        <is>
-          <t>Inferencia Causal &amp; Modelamiento Decisional para Negocios</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="inlineStr">
-        <is>
-          <t>Doctor en Economía Cuantitativa o Estadística Aplicada, con vasta trayectoria laboral en diseño de experimentos de alta precisión de comportamiento de consumo e inferencia para industrias digitales de primer nivel.</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Experto en Regulación de Datos y XAI (Explainable AI)</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Gobernanza de Datos, Ética en IA &amp; Algoritmos Explicables (XAI)</t>
-        </is>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>Ph.D. o Magíster en Ética Aplicada, Derecho de TI o Ciencia de Datos, que haya liderado procesos de auditoría del comportamiento ético de algoritmos de decisión de otorgamiento de crédito o contratación en entidades de la Unión Europea o América Latina.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
-      <c r="G58" s="13" t="n"/>
-      <c r="H58" s="13" t="n"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="23" t="inlineStr">
-        <is>
-          <t>ESTADO DE APROBACIÓN</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>PENDIENTE_REVISION (Versión v1)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2" t="n"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
-        <is>
-          <t>AVAL / DECISIÓN DIRECTIVA</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Pendiente de Visto Bueno por Comité Curricular</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="23" t="inlineStr">
-        <is>
-          <t>FECHA ÚLTIMA DECISIÓN</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>En proceso de revisión</t>
         </is>
       </c>
       <c r="D61" s="2" t="n"/>
